--- a/slidedeck/data/model_slide_data_static.xlsx
+++ b/slidedeck/data/model_slide_data_static.xlsx
@@ -88009,7 +88009,7 @@
         <v>187</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06287526767272489</v>
+        <v>0.0628752676727249</v>
       </c>
       <c r="E2" t="n">
         <v>0.08219780219780219</v>
@@ -88078,7 +88078,7 @@
         <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1308153787660015</v>
+        <v>0.1308153787660014</v>
       </c>
       <c r="E5" t="n">
         <v>0.1468131868131868</v>
@@ -88844,7 +88844,7 @@
         <v>0.123897764926482</v>
       </c>
       <c r="C10" t="n">
-        <v>0.009012526415618038</v>
+        <v>0.009012526415618073</v>
       </c>
       <c r="D10" t="n">
         <v>74228.07915513657</v>
@@ -88856,19 +88856,19 @@
         <v>15763620233.57781</v>
       </c>
       <c r="G10" t="n">
-        <v>906066008.721676</v>
+        <v>906066008.7216766</v>
       </c>
       <c r="H10" t="n">
-        <v>283.3895051454633</v>
+        <v>283.3895051454634</v>
       </c>
       <c r="I10" t="n">
-        <v>44.36318046071679</v>
+        <v>44.3631804607168</v>
       </c>
       <c r="J10" t="n">
         <v>0.7749412139402325</v>
       </c>
       <c r="K10" t="n">
-        <v>0.007476574926457983</v>
+        <v>0.007476574926457888</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
